--- a/artfynd/A 38385-2021 artfynd.xlsx
+++ b/artfynd/A 38385-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38385-2021 artfynd.xlsx
+++ b/artfynd/A 38385-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,40 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79704501</v>
+        <v>98225115</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -718,17 +717,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gruvmossen Gammelbo, Vstm</t>
+          <t>Gruvmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522310.9214546402</v>
+        <v>522259</v>
       </c>
       <c r="R2" t="n">
-        <v>6629275.81508637</v>
+        <v>6629380</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +754,9 @@
           <t>2019-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79704688</v>
+        <v>79704635</v>
       </c>
       <c r="B3" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522319.3275176795</v>
+        <v>522259</v>
       </c>
       <c r="R3" t="n">
-        <v>6629303.039569436</v>
+        <v>6629390</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,19 +856,9 @@
           <t>2019-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79704635</v>
+        <v>79704701</v>
       </c>
       <c r="B4" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522259.3243207848</v>
+        <v>522306</v>
       </c>
       <c r="R4" t="n">
-        <v>6629390.23951225</v>
+        <v>6629354</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,19 +958,9 @@
           <t>2019-08-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79704933</v>
+        <v>98657566</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,39 +999,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gruvmossen Gammelbo, Vstm</t>
+          <t>Gruvmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522259.3243207848</v>
+        <v>522261</v>
       </c>
       <c r="R5" t="n">
-        <v>6629390.23951225</v>
+        <v>6629385</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,22 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,19 +1086,18 @@
           <t>Linn Svensson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79704701</v>
+        <v>79704572</v>
       </c>
       <c r="B6" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522305.9171531124</v>
+        <v>522326</v>
       </c>
       <c r="R6" t="n">
-        <v>6629353.784144618</v>
+        <v>6629325</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,22 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,64 +1196,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98225115</v>
+        <v>79704688</v>
       </c>
       <c r="B7" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gruvmossen, Vstm</t>
+          <t>Gruvmossen Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522259.3845450281</v>
+        <v>522319</v>
       </c>
       <c r="R7" t="n">
-        <v>6629380.175668161</v>
+        <v>6629303</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,19 +1268,9 @@
           <t>2019-08-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,15 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98351210</v>
+        <v>98657596</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,42 +1309,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbo, Vstm</t>
+          <t>Gruvmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522309.1859892046</v>
+        <v>522331</v>
       </c>
       <c r="R8" t="n">
-        <v>6629397.079948785</v>
+        <v>6629334</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,39 +1370,30 @@
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1509,15 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98351213</v>
+        <v>98351174</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,39 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522328.2620385872</v>
+        <v>522322</v>
       </c>
       <c r="R9" t="n">
-        <v>6629242.202899797</v>
+        <v>6629353</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1587,19 +1472,9 @@
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-05-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98657559</v>
+        <v>98351176</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,40 +1516,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gruvmossen, Vstm</t>
+          <t>Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522316.0343655373</v>
+        <v>522330</v>
       </c>
       <c r="R10" t="n">
-        <v>6629431.842269753</v>
+        <v>6629357</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,40 +1573,29 @@
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1750,15 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98657610</v>
+        <v>98351178</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,40 +1617,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gruvmossen, Vstm</t>
+          <t>Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522319.170343317</v>
+        <v>522331</v>
       </c>
       <c r="R11" t="n">
-        <v>6629413.242489344</v>
+        <v>6629375</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1826,40 +1674,29 @@
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1870,15 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98657566</v>
+        <v>98657605</v>
       </c>
       <c r="B12" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,21 +1718,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1914,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>522261.3706337276</v>
+        <v>522325</v>
       </c>
       <c r="R12" t="n">
-        <v>6629385.219659531</v>
+        <v>6629386</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1947,19 +1779,9 @@
           <t>2021-05-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-05-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,6 +1806,843 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>98657618</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gruvmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>522336</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6629433</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>79704501</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gruvmossen Gammelbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>522311</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6629276</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>79704598</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gruvmossen Gammelbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>522318</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6629439</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>98657559</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gruvmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>522316</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6629432</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>98657610</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gruvmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>522319</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6629413</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>79704756</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gruvmossen Gammelbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>522259</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6629390</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>98351210</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gammelbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>522309</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6629397</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>98351213</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gammelbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>522328</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6629242</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
